--- a/daily_matches/job_matches_2026-06-05.xlsx
+++ b/daily_matches/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>Data Scientist / Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, S3, Glue, Athena, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69d5a1a971e22e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Radian Group Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>25.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, AKS, CI/CD, Git, Databricks, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Tergar International</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL</t>
+          <t>Data Scientist, RAG, Glue, Redshift, Docker, CI/CD, Terraform, Git, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b89feeb112329ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eec213f6c00cd9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Platform &amp; Backend Focus)</t>
+          <t>AI/ML Engineer with Drone Imagery</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, AKS, CI/CD, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, OpenCV, YOLO, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e87a97e8641f456</t>
+          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. AI Automation Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, Gemini, Copilot, Jenkins, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, FAISS, Pinecone, S3, Glue, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6e45820c99764d</t>
+          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer-1</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
+          <t>Data Scientist, RAG, FAISS, Pinecone, S3, Glue, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33b30dfb96c1e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Solutions Developer / Data Scientist II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HDR</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1785449414d62f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Infrastructure Operations Engineer Greensboro, NC</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24accb0bf19fa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infrastructure Operations Engineer Greensboro, NC</t>
+          <t>Data Scientist Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56b109dffe639e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=60efe3ffc51f66b2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer – DevOps / MLOps Engineer</t>
+          <t>Data Scientist Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chefman</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fe7a19c1622760</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e579067dad4a5a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
+          <t>Data Scientist Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7beb55455531c586</t>
+          <t>https://www.indeed.com/viewjob?jk=e1bd74c751e7dc20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Data Scientist Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df77ae57790bb91</t>
+          <t>https://www.indeed.com/viewjob?jk=d568802494117bca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analyst, Lending</t>
+          <t>Data Scientist Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, BigQuery, Tableau, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,2177 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0390095ba29fbace</t>
+          <t>https://www.indeed.com/viewjob?jk=5d46ac00471453aa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Moorestown, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40ddfd7f9dc10d73</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=293049bb2c1516cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5f2a0cec6f18d3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7b87f34df60fa13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05187c291a295e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc9cf377f77f2678</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cc144877c27f121</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce32e02c83d1b84a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b5d37a3ed13197d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31c343149580f1fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4a52d56f59e2971</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a66c3291e470d396</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af8050593b180b5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=643767fdebbc2208</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2852edc388bdca2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=836d150c4c19725f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8888d8806ba6165</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78d2736bc242e4a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4250034b23eb5e30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a7dda2bb261a637</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=554cebf19bae43c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b032a4b683d2a083</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8ec55115463bae1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b854ebc509a23ff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db024c421446e64f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba627e1bdc341691</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37716f32fb2c2241</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ab8a6ed68c75845</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33114a527c422ffa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c8a262369b2a0f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Scientist Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c6ddd3e4f11c8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nexxen</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a96178a2a524d96e</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer Hybrid</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>David's Bridal</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, EC2, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=746f9f95b4a4ccce</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI Technology Support Engineer/Analyst</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Keras, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c1559ab04a869e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cayuse Holdings</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Cortex, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbd71fed3e29eab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Managed Services Engineer III</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Science - AI Document Understanding, Co-op</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ancestry</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Hugging Face, S3, EC2, Python, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa2ab1020e019bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Manscaped</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Authorization Team</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PagerDuty</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Kafka, MySQL, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9026373eecbd3c8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Engineer - Agent Automation</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f9e4939e51aa462</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Major League Baseball (MLB)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3c485edfa7ab169</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Agentic Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=364f8e08019cdeb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer II</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Chewy</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, FastAPI, Tableau, Power BI, Quicksight, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad2c5d91879b9718</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Engineer III (Platform)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MAPFRE Insurance</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Webster, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Glue, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Algorithm Engineer - Deep Learning</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1594b3a2e78e7995</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Sr. DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Meazure Learning</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a8ab4c51db6d251</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Java (AMS)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Ensono</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b68203988208d24b</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior AI Expert Software Engineer – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Git, PostgreSQL, MySQL, MongoDB, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8631772e7f6c0392</t>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1216782c0a1b2b7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Algorithm/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Elbit Systems of America</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c204d3b9d97471f</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Algorithm/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Elbit Systems of America</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39efa0d30333eab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Chefman</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=629a6ffa6c8fe733</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer, Security</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>David AI</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2503c1c410dfa45e</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=072e51c4bffec3aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Scientist - Materials Characterization, Analytical Sciences &amp; AI Agents</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EAG Laboratories</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7c09db95ec9f066</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Advatix</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, FastAPI, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8903cd04f9b5666e</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Advatix</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, FastAPI, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b8c99d0e4a3ae49</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=863bc7b8b01f52dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Scientist - Network Strategy</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05e2ec69417e3f6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Cloud Microservices</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Anderson Merchandisers</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d66749a3b3342226</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-05.xlsx
+++ b/daily_matches/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Analytics Engineer</t>
+          <t>AI Engineer — RapidCanvas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>David Joseph &amp; Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, S3, Glue, Athena, Redshift</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, XGBoost, LightGBM, MLflow, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69d5a1a971e22e</t>
+          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Radian Group Inc.</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.6</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM, CatBoost</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
+          <t>https://www.indeed.com/viewjob?jk=0ecd0ef97923c7bb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tergar International</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Redshift, Docker, CI/CD, Terraform, Git, Redshift, PySpark</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eec213f6c00cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=cf52f831ff19b44f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with Drone Imagery</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Qcells</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, OpenCV, YOLO, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce1c9d6a997f571</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>IT AI ENGINEER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FAISS, Pinecone, S3, Glue, CI/CD, Terraform, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, FastAPI, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
+          <t>https://www.indeed.com/viewjob?jk=91e0fd3a63ffa4bb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Software Engineer III - Python Developer/AWS/Kafka</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FAISS, Pinecone, S3, Glue, CI/CD, Terraform, Snowflake, Databricks</t>
+          <t>LangChain, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=45e39bb855510244</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CCS Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, MLflow, Docker, Kubernetes, CI/CD, PySpark</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, MLflow, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=81d3b9f579b9fdfc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
+          <t>Data Scientist, RAG, Copilot, Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
+          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>Machine Learning Engineer, RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60efe3ffc51f66b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>S3, Glue, Athena, Redshift, Data Lake, Kinesis, Redshift, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,1284 +811,1284 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e579067dad4a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1bd74c751e7dc20</t>
+          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d568802494117bca</t>
+          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d46ac00471453aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40ddfd7f9dc10d73</t>
+          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293049bb2c1516cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f2a0cec6f18d3a</t>
+          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b87f34df60fa13</t>
+          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05187c291a295e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9cf377f77f2678</t>
+          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc144877c27f121</t>
+          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce32e02c83d1b84a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5d37a3ed13197d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c343149580f1fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a52d56f59e2971</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66c3291e470d396</t>
+          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8050593b180b5d</t>
+          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=643767fdebbc2208</t>
+          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2852edc388bdca2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=836d150c4c19725f</t>
+          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8888d8806ba6165</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d2736bc242e4a2</t>
+          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4250034b23eb5e30</t>
+          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7dda2bb261a637</t>
+          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554cebf19bae43c7</t>
+          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b032a4b683d2a083</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ec55115463bae1</t>
+          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b854ebc509a23ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db024c421446e64f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba627e1bdc341691</t>
+          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37716f32fb2c2241</t>
+          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ab8a6ed68c75845</t>
+          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33114a527c422ffa</t>
+          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8a262369b2a0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist Engineer - SFL Scientific</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6ddd3e4f11c8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexxen</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a96178a2a524d96e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer Hybrid</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, EC2, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746f9f95b4a4ccce</t>
+          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Technology Support Engineer/Analyst</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Keras, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1559ab04a869e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Databricks, Python, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,217 +2166,217 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cortex, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI ML Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbd71fed3e29eab2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Managed Services Engineer III</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Science - AI Document Understanding, Co-op</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ancestry</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Hugging Face, S3, EC2, Python, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ab1020e019bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
+          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II - Authorization Team</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PagerDuty</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Kafka, MySQL, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,229 +2386,229 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9026373eecbd3c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Engineer - Agent Automation</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, PyTorch, Docker, Kubernetes, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9e4939e51aa462</t>
+          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Major League Baseball (MLB)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3c485edfa7ab169</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Agentic Software Engineer II</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f8e08019cdeb6</t>
+          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, FastAPI, Tableau, Power BI, Quicksight, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad2c5d91879b9718</t>
+          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer III (Platform)</t>
+          <t>URBN Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Glue, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>RAG, Pinecone, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Algorithm Engineer - Deep Learning</t>
+          <t>Java Spring Boot Developer - Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1594b3a2e78e7995</t>
+          <t>https://www.indeed.com/viewjob?jk=8111959a40bb4818</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Pre-Sales Solutions Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Meazure Learning</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,29 +2621,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a8ab4c51db6d251</t>
+          <t>https://www.indeed.com/viewjob?jk=213fb87605c12838</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Java (AMS)</t>
+          <t>Full Stack Developer (Laravel &amp; React)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Virtual Moving Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Optimization</t>
+          <t>RAG, Copilot, S3, EC2, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b68203988208d24b</t>
+          <t>https://www.indeed.com/viewjob?jk=f091ad1af56bfa6b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Expert Software Engineer – Healthcare Analytics</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,81 +2687,81 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Optimization</t>
+          <t>CI/CD, Git, NoSQL, Tableau, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1216782c0a1b2b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Algorithm/AI Engineer</t>
+          <t>AI Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Elbit Systems of America</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c204d3b9d97471f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c1c6c99e7d17396</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Algorithm/AI Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Elbit Systems of America</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Databricks, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39efa0d30333eab1</t>
+          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Chefman</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629a6ffa6c8fe733</t>
+          <t>https://www.indeed.com/viewjob?jk=41d0e7f2e21b5f38</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer, Security</t>
+          <t>Senior Software Engineer (AI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>David AI</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2503c1c410dfa45e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5dc92fff82a2a4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Product Engineer (Remote Opportunity)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,227 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072e51c4bffec3aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Scientist - Materials Characterization, Analytical Sciences &amp; AI Agents</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>EAG Laboratories</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c09db95ec9f066</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Advatix</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, FastAPI, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8903cd04f9b5666e</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Advatix</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, FastAPI, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8c99d0e4a3ae49</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sr. Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>PlayStation</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=863bc7b8b01f52dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Data Scientist - Network Strategy</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05e2ec69417e3f6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Cloud Microservices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Anderson Merchandisers</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d66749a3b3342226</t>
+          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-05.xlsx
+++ b/daily_matches/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, XGBoost, MLflow, Databricks, PySpark, Hadoop, Tableau, Matplotlib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f3b09a9c1f5b31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Branch</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4996d675c7dec51</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer (USC &amp; GC only - Max $75/hr W2)</t>
+          <t>Senior Software Engineer, AI Platform Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lenmar Consulting</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Athena, Redshift, Git, Snowflake, Databricks, Redshift, Tableau, Quicksight, Python</t>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a137ccd45eda03e</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b2e2ae3f895738</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Solutions Architect – Azure Databricks</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MINDBRIDGE SOLUTIONS INC</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CI/CD, Terraform, Snowflake, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2e06388f458abb1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AlohaABA</t>
+          <t>Synstack Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Hugging Face, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>Data Lake, Databricks, PySpark, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7e3326fa7f1d58c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f22b99fcc46a1ed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist - People Analytics</t>
+          <t>Data Scientist, Modeler</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Teleflora</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, MLflow, Git, BigQuery, Tableau, Python, SQL</t>
+          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d645ab1f896a37</t>
+          <t>https://www.indeed.com/viewjob?jk=06e1f5fdf42ea33d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Azure SME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Epathusa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8402603cef9b987a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0f4baba9aa516e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ICT Senior Officer - Software Development</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>United Nations Office for Project Services</t>
+          <t>Equus Workforce Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713674a7664ac1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d1984fcf8ba0e2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II - AI Assistant Enablement</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Git, NoSQL, SQL, R, Java, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, AKS, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a45ad2f7432b95f</t>
+          <t>https://www.indeed.com/viewjob?jk=a925345e12c6666b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rice Engineering</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Git, NoSQL, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, S3, Glue, Data Lake, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0634670c33ed94a8</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATHENE</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Glue, Athena, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Docker, Git, Hadoop, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36eef6c910bf1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Penlink</t>
+          <t>Revenue.io</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+          <t>RAG, AKS, CI/CD, Jenkins, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d74c574d000fbb5</t>
+          <t>https://www.indeed.com/viewjob?jk=7734bed616f7d087</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Splunk Platform Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Netbuilder</t>
+          <t>Ellucian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b5030259fe586f</t>
+          <t>https://www.indeed.com/viewjob?jk=95b3f6bb992b928d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, S3, AKS, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba91fdc1e9a98f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f4d47ed69df8ad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, TensorFlow, PyTorch, CI/CD, Databricks, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44d0cb03b54d0fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8fdbb28b048c3890</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carbo Ceramics, LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,77 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d10e8fe29e20e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d95054cb2877ab7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Identity and Access Management Consultant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Collective Insights</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da7dfd029865b134</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Developer Intern</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>iCatalyst</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e7bff63b3620d3c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-05.xlsx
+++ b/daily_matches/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, XGBoost, MLflow, Databricks, PySpark, Hadoop, Tableau, Matplotlib</t>
+          <t>AI Engineer, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f3b09a9c1f5b31</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b877f69f2d40c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI Platform Engineering</t>
+          <t>BI and AI Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Trianz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, Python, R, Java</t>
+          <t>S3, Glue, Athena, Redshift, Git, Snowflake, Redshift, Tableau, Power BI, Quicksight</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b2e2ae3f895738</t>
+          <t>https://www.indeed.com/viewjob?jk=9063c5940585caea</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Redshift, BigQuery, Data Lake, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Hadoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2e06388f458abb1</t>
+          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Synstack Technologies</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Lake, Databricks, PySpark, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Hadoop, Tableau, Power BI, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f22b99fcc46a1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d957baf04ddddb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist, Modeler</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Teleflora</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e1f5fdf42ea33d</t>
+          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure SME</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Epathusa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0f4baba9aa516e</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equus Workforce Solutions</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Git, Snowflake, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d1984fcf8ba0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=301853b8fccc1809</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Assistant Enablement</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, AKS, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925345e12c6666b</t>
+          <t>https://www.indeed.com/viewjob?jk=cedcd207613bb4ad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Data Lake, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
+          <t>https://www.indeed.com/viewjob?jk=d34924c7fa34c06a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Data Engineer - AI, Agents, &amp; Context - Revenue Cycle (Associate)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Roseville, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Git, Hadoop, NoSQL, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Pinecone, Snowflake, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
+          <t>https://www.indeed.com/viewjob?jk=981ec3014106c4d1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Revenue.io</t>
+          <t>LinTech Global, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, Jenkins, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7734bed616f7d087</t>
+          <t>https://www.indeed.com/viewjob?jk=105171f98b8f6a13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ellucian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95b3f6bb992b928d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f4d47ed69df8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=129266e52e9bbad8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Data Scientist, Modeler</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Teleflora</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, CI/CD, Databricks, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fdbb28b048c3890</t>
+          <t>https://www.indeed.com/viewjob?jk=e869e8c3406b2a3d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Data Scientist, Modeler</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Teleflora</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Paragould, AR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95054cb2877ab7c</t>
+          <t>https://www.indeed.com/viewjob?jk=07629f41c574e986</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Identity and Access Management Consultant</t>
+          <t>Azure SME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Collective Insights</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,497 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7dfd029865b134</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e9ea436df4c98f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Developer Intern</t>
+          <t>Data Engineer - AI, Agents, &amp; Context - Clinical (Sr. Associate)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iCatalyst</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Pinecone, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fbc491caa5d5b3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Test Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=042944e8a3e3c1f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Client Platform Engineer, AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nextdoor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, Copilot, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd4fa587bb217e39</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fe7317e8a9bbf9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Science Analyst - Growth, Marketing &amp; Sales</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Git, Hadoop, MongoDB, NoSQL, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6082797ea46b9d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=386d21d963baf0d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef64c8f780e6b55e</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7bff63b3620d3c</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a4c5223316a9df0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer, GTM AI - Python</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Telnyx</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=221947144198facb</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer, GTM AI - Python</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Telnyx</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70378b781fd07284</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. Azure Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Broomfield, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3a415357996d46e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Flexential</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Centennial, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=029ef21b34253f89</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - MET</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd9402522c7a5517</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AWS SME</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Skywalk Global</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3aced7dde90b2668</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-05.xlsx
+++ b/daily_matches/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b877f69f2d40c</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BI and AI Automation Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Redshift, Git, Snowflake, Redshift, Tableau, Power BI, Quicksight</t>
+          <t>RAG, BigQuery, Dataflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063c5940585caea</t>
+          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Data Lake, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Hadoop</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1a529beb32ef3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>STIO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Hadoop, Tableau, Power BI, Matplotlib, Seaborn</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d957baf04ddddb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee76c681f5b25025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>STIO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Power BI, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b2388182ed216637</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>STIO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jackson, WY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, PySpark, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
+          <t>https://www.indeed.com/viewjob?jk=bd643bfc419376c2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>STIO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301853b8fccc1809</t>
+          <t>https://www.indeed.com/viewjob?jk=17ea106362a34a69</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, SQL, R</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cedcd207613bb4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=02f7a82ae76adde3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34924c7fa34c06a</t>
+          <t>https://www.indeed.com/viewjob?jk=47956bbc84ca4407</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - AI, Agents, &amp; Context - Revenue Cycle (Associate)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, Snowflake, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, PyTorch, Docker, Kubernetes, Terraform, Git, NoSQL, Polars, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=981ec3014106c4d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LinTech Global, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Databricks, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105171f98b8f6a13</t>
+          <t>https://www.indeed.com/viewjob?jk=7052541ef709e6b8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI ML Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f9e1bd052f4299</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Development Engineer in Test II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129266e52e9bbad8</t>
+          <t>https://www.indeed.com/viewjob?jk=cf524b917415e3a5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist, Modeler</t>
+          <t>Software Development Engineer in Test II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Teleflora</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e869e8c3406b2a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=eed759f74ea66bf0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist, Modeler</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Teleflora</t>
+          <t>Fabric Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paragould, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, Prompt Engineering, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07629f41c574e986</t>
+          <t>https://www.indeed.com/viewjob?jk=8ce9354b05ea6bb9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure SME</t>
+          <t>DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>Happy Returns, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3e9ea436df4c98f</t>
+          <t>https://www.indeed.com/viewjob?jk=e49315218b95b8ca</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - AI, Agents, &amp; Context - Clinical (Sr. Associate)</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, BigQuery, Terraform, Git, BigQuery, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fbc491caa5d5b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Azure SME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=042944e8a3e3c1f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e49d4d8d8d783b9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Client Platform Engineer, AI &amp; Automation</t>
+          <t>Cybersecurity Code Test Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nextdoor</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Copilot, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd4fa587bb217e39</t>
+          <t>https://www.indeed.com/viewjob?jk=fb7c4b988fb654d1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe7317e8a9bbf9b</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb3d3091c8bade4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Growth, Marketing &amp; Sales</t>
+          <t>Senior Data Engineer, AI &amp; Context Platform - Healthcare Insights - Rev Cycle OR Clinical Team (2 Openings)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Git, Hadoop, MongoDB, NoSQL, Tableau, Python, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Pinecone, CI/CD, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6082797ea46b9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=039b9f101cc70d2f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Addepar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, R</t>
+          <t>Kinesis, Terraform, Snowflake, Databricks, Kafka, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=386d21d963baf0d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac99f352a5386dc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI Researcher / ML Engineer (ASR &amp; Speech Specialist)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lilt- Lega Italiana per la Lotta contro i Tumori</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, R</t>
+          <t>Machine Learning Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef64c8f780e6b55e</t>
+          <t>https://www.indeed.com/viewjob?jk=46da7d91c602039c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Researcher / ML Engineer (ASR &amp; Speech Specialist)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Lilt- Lega Italiana per la Lotta contro i Tumori</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a4c5223316a9df0</t>
+          <t>https://www.indeed.com/viewjob?jk=025012a9b207eae4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, GTM AI - Python</t>
+          <t>AI Researcher / ML Engineer (ASR &amp; Speech Specialist)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Telnyx</t>
+          <t>Lilt- Lega Italiana per la Lotta contro i Tumori</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221947144198facb</t>
+          <t>https://www.indeed.com/viewjob?jk=2224e13a140e8076</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, GTM AI - Python</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Telnyx</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70378b781fd07284</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Azure Infrastructure Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Copilot, S3, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a415357996d46e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cb5c038412060b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data &amp; AI Solution Engineer</t>
+          <t>Sr Software Development Engineer in Test (Sr SDET)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Flexential</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029ef21b34253f89</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4e1454d5654ac9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - MET</t>
+          <t>Sr Software Development Engineer in Test (Sr SDET)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9402522c7a5517</t>
+          <t>https://www.indeed.com/viewjob?jk=46418df7a9b1b23b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS SME</t>
+          <t>Sr Software Development Engineer in Test (Sr SDET)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,192 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0320e6e3f1f912ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer in Test (Sr SDET)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba8202e508d36123</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer in Test (Sr SDET)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Aliso Viejo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ce8dee5d02267c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Heaven Hill</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Data Lake, Git, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a45b9b9f90c2f92e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior GIS Data Analyst (Utilities)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MCKIM &amp; CREED</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Power BI, Matplotlib, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8c53558337d171</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AWS SME</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Infoorigin Inc</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3aced7dde90b2668</t>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bc198bf076a51fc</t>
         </is>
       </c>
     </row>
